--- a/data/trans_orig/IP16B05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B05-Edad-trans_orig.xlsx
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
